--- a/Grafik_CCEE_SLIVEN1_06_08_2026.xlsx
+++ b/Grafik_CCEE_SLIVEN1_06_08_2026.xlsx
@@ -1629,8 +1629,10 @@
       <c r="B49" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C49" s="11" t="n">
-        <v>0</v>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D49" s="5" t="n">
         <v>0</v>
@@ -1649,8 +1651,10 @@
       <c r="B50" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C50" s="11" t="n">
-        <v>0</v>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D50" s="5" t="n">
         <v>0</v>
@@ -1669,8 +1673,10 @@
       <c r="B51" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C51" s="11" t="n">
-        <v>0</v>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D51" s="5" t="n">
         <v>0</v>
@@ -1689,8 +1695,10 @@
       <c r="B52" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C52" s="11" t="n">
-        <v>0</v>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D52" s="5" t="n">
         <v>0</v>
@@ -1709,8 +1717,10 @@
       <c r="B53" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C53" s="11" t="n">
-        <v>0</v>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D53" s="5" t="n">
         <v>0</v>
@@ -1729,8 +1739,10 @@
       <c r="B54" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C54" s="11" t="n">
-        <v>0</v>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D54" s="5" t="n">
         <v>0</v>
@@ -1749,8 +1761,10 @@
       <c r="B55" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C55" s="11" t="n">
-        <v>0</v>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D55" s="5" t="n">
         <v>0</v>
@@ -1769,8 +1783,10 @@
       <c r="B56" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C56" s="11" t="n">
-        <v>0</v>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D56" s="5" t="n">
         <v>0</v>
@@ -1789,8 +1805,10 @@
       <c r="B57" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C57" s="11" t="n">
-        <v>0</v>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D57" s="5" t="n">
         <v>0</v>
@@ -1949,10 +1967,8 @@
       <c r="B65" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C65" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D65" s="5" t="n">
         <v>0</v>
@@ -1971,10 +1987,8 @@
       <c r="B66" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C66" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D66" s="5" t="n">
         <v>0</v>
@@ -1993,10 +2007,8 @@
       <c r="B67" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C67" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D67" s="5" t="n">
         <v>0</v>
@@ -2015,10 +2027,8 @@
       <c r="B68" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C68" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D68" s="5" t="n">
         <v>0</v>
@@ -2037,10 +2047,8 @@
       <c r="B69" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C69" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D69" s="5" t="n">
         <v>0</v>
@@ -2059,10 +2067,8 @@
       <c r="B70" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C70" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D70" s="5" t="n">
         <v>0</v>
@@ -2081,10 +2087,8 @@
       <c r="B71" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C71" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D71" s="5" t="n">
         <v>0</v>
@@ -2103,10 +2107,8 @@
       <c r="B72" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C72" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>0</v>
@@ -2125,10 +2127,8 @@
       <c r="B73" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C73" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D73" s="5" t="n">
         <v>0</v>

--- a/Grafik_CCEE_SLIVEN1_06_08_2026.xlsx
+++ b/Grafik_CCEE_SLIVEN1_06_08_2026.xlsx
@@ -1629,10 +1629,8 @@
       <c r="B49" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C49" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D49" s="5" t="n">
         <v>0</v>
@@ -1651,10 +1649,8 @@
       <c r="B50" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C50" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C50" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>0</v>
@@ -1673,10 +1669,8 @@
       <c r="B51" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C51" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D51" s="5" t="n">
         <v>0</v>
@@ -1695,10 +1689,8 @@
       <c r="B52" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C52" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>0</v>
@@ -1717,10 +1709,8 @@
       <c r="B53" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C53" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>0</v>
@@ -1739,10 +1729,8 @@
       <c r="B54" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C54" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>0</v>
@@ -1761,10 +1749,8 @@
       <c r="B55" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C55" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C55" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>0</v>
@@ -1783,10 +1769,8 @@
       <c r="B56" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C56" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>0</v>
@@ -1805,10 +1789,8 @@
       <c r="B57" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C57" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D57" s="5" t="n">
         <v>0</v>
@@ -1967,8 +1949,10 @@
       <c r="B65" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C65" s="11" t="n">
-        <v>0</v>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D65" s="5" t="n">
         <v>0</v>
@@ -1987,8 +1971,10 @@
       <c r="B66" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C66" s="11" t="n">
-        <v>0</v>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D66" s="5" t="n">
         <v>0</v>
@@ -2007,8 +1993,10 @@
       <c r="B67" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C67" s="11" t="n">
-        <v>0</v>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D67" s="5" t="n">
         <v>0</v>
@@ -2027,8 +2015,10 @@
       <c r="B68" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C68" s="11" t="n">
-        <v>0</v>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D68" s="5" t="n">
         <v>0</v>
@@ -2047,8 +2037,10 @@
       <c r="B69" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C69" s="11" t="n">
-        <v>0</v>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D69" s="5" t="n">
         <v>0</v>
@@ -2067,8 +2059,10 @@
       <c r="B70" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C70" s="11" t="n">
-        <v>0</v>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D70" s="5" t="n">
         <v>0</v>
@@ -2087,8 +2081,10 @@
       <c r="B71" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C71" s="11" t="n">
-        <v>0</v>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D71" s="5" t="n">
         <v>0</v>
@@ -2107,8 +2103,10 @@
       <c r="B72" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C72" s="11" t="n">
-        <v>0</v>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D72" s="5" t="n">
         <v>0</v>
@@ -2127,8 +2125,10 @@
       <c r="B73" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C73" s="11" t="n">
-        <v>0</v>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D73" s="5" t="n">
         <v>0</v>
@@ -2323,11 +2323,13 @@
       <c r="B82" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C82" s="11" t="n">
-        <v>0</v>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E82" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C82+D82,0))),MIN(1800,MAX(0,D82)))</f>
@@ -2343,11 +2345,13 @@
       <c r="B83" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C83" s="11" t="n">
-        <v>0</v>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E83" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C83+D83,0))),MIN(1800,MAX(0,D83)))</f>
@@ -2363,11 +2367,13 @@
       <c r="B84" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C84" s="11" t="n">
-        <v>0</v>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E84" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C84+D84,0))),MIN(1800,MAX(0,D84)))</f>
@@ -2383,11 +2389,13 @@
       <c r="B85" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C85" s="11" t="n">
-        <v>0</v>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E85" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C85+D85,0))),MIN(1800,MAX(0,D85)))</f>
@@ -2403,11 +2411,13 @@
       <c r="B86" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C86" s="11" t="n">
-        <v>0</v>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E86" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C86+D86,0))),MIN(1800,MAX(0,D86)))</f>
@@ -2423,11 +2433,13 @@
       <c r="B87" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C87" s="11" t="n">
-        <v>0</v>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E87" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C87+D87,0))),MIN(1800,MAX(0,D87)))</f>
@@ -2443,11 +2455,13 @@
       <c r="B88" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>0</v>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E88" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C88+D88,0))),MIN(1800,MAX(0,D88)))</f>
@@ -2463,11 +2477,13 @@
       <c r="B89" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C89" s="11" t="n">
-        <v>0</v>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E89" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C89+D89,0))),MIN(1800,MAX(0,D89)))</f>
@@ -2483,11 +2499,13 @@
       <c r="B90" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C90" s="11" t="n">
-        <v>0</v>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E90" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C90+D90,0))),MIN(1800,MAX(0,D90)))</f>
@@ -2523,13 +2541,11 @@
       <c r="B92" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C92" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C92" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E92" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C92+D92,0))),MIN(1800,MAX(0,D92)))</f>
@@ -2545,13 +2561,11 @@
       <c r="B93" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C93" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E93" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C93+D93,0))),MIN(1800,MAX(0,D93)))</f>
@@ -2567,13 +2581,11 @@
       <c r="B94" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C94" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C94" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E94" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C94+D94,0))),MIN(1800,MAX(0,D94)))</f>
@@ -2589,13 +2601,11 @@
       <c r="B95" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C95" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C95" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E95" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C95+D95,0))),MIN(1800,MAX(0,D95)))</f>
@@ -2611,13 +2621,11 @@
       <c r="B96" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C96" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C96" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E96" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C96+D96,0))),MIN(1800,MAX(0,D96)))</f>
@@ -2633,13 +2641,11 @@
       <c r="B97" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C97" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C97" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E97" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C97+D97,0))),MIN(1800,MAX(0,D97)))</f>
@@ -2655,13 +2661,11 @@
       <c r="B98" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C98" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C98" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E98" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C98+D98,0))),MIN(1800,MAX(0,D98)))</f>
@@ -2677,13 +2681,11 @@
       <c r="B99" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C99" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C99" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E99" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C99+D99,0))),MIN(1800,MAX(0,D99)))</f>
@@ -2699,13 +2701,11 @@
       <c r="B100" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="C100" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C100" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E100" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C100+D100,0))),MIN(1800,MAX(0,D100)))</f>
